--- a/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrange.xlsx
+++ b/jpcore-r4/feature/ImagingStudyTest/StructureDefinition-jp-medicationrange.xlsx
@@ -266,7 +266,7 @@
 </t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 rng-2:存在する場合、低い値は高よりも低い値を持つものとします / If present, low SHALL have a lower value than high {low.empty() or high.empty() or (low &lt;= high)}</t>
   </si>
   <si>
@@ -331,7 +331,7 @@
     <t>Element.extension</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
@@ -351,7 +351,7 @@
     <t>薬剤に関する簡易的な数量と単位を定めている。ValueおよびCodeを必須とし、comparatorは記述不可。単位についてはMERIT9医薬品単位略号の利用を推進している。(**SHOULD**)</t>
   </si>
   <si>
-    <t>ele-1:すべてのFHIR要素には、@valueまたは子供が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 qty-3:ユニットのコードが存在する場合、システムも存在するものとします / If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:コンパレータは、単純なQuantityで使用されません / The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
